--- a/Manual-Testing/Q3_TestCases.xlsx
+++ b/Manual-Testing/Q3_TestCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright\ecommerce-automation-test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright\ecommerce-automation-test\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804DE9C4-0132-463E-A116-DAC594AAE949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187F8240-B95B-4046-9991-07FD235A176B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -60,18 +60,12 @@
     <t>TC_001</t>
   </si>
   <si>
-    <t>Login</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Verify that a locked-out user cannot log in and receives the correct error message.</t>
-  </si>
-  <si>
     <t>Preconditions</t>
   </si>
   <si>
@@ -79,57 +73,16 @@
   </si>
   <si>
     <t>Severity</t>
-  </si>
-  <si>
-    <t>1. Open SauceDemo Login Page
-2. Enter username: locked_out_user
-3. Enter password: secret_sauce
-4. Click the Login button.</t>
   </si>
   <si>
     <t>1. User is on the SauceDemo login page.
 2. Internet connection is active.</t>
   </si>
   <si>
-    <t>Username
-locked_out_user
-Password
-secret_sauce</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">User should not be logged in.
-The following error message should be displayed:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Epic sadface: Sorry, this user has been locked out.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Error message displayed successfully:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Epic sadface: Sorry, this user has been locked out.</t>
-    </r>
+    <t>Verify  successful order message and logout</t>
+  </si>
+  <si>
+    <t>Thank you for your order!</t>
   </si>
   <si>
     <r>
@@ -152,7 +105,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Verify Locked Out User Login Error
+Login with performance_glitch_user and reset the App State. Then filter by name (Z to A) and select the first product into the cart. Then navigate up to the final checkout page and verify all the products' names and the total price. Then finish the purchase journey and verify the successful order message. Then, reset the App State again and log out.
 </t>
     </r>
     <r>
@@ -175,9 +128,42 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-SauceDemo
+https://www.saucedemo.com/
 </t>
     </r>
+  </si>
+  <si>
+    <t>CartToCheckout</t>
+  </si>
+  <si>
+    <t>Authentication
+Username
+performance_glitch_user 
+Password
+secret_sauce
+Checkout
+First Name: Saddam
+Last Name: Hossain
+ZIP: 1230</t>
+  </si>
+  <si>
+    <t>1. Open SauceDemo Login Page
+2. Enter username: standard_user
+3. Enter password: secret_sauce
+4. Click the Login button.
+5. Click huburger menu
+6. Click Reset App State
+7.  Filter by name (Z to A) 
+8. Add First Item in Cart
+8. Click Cart Menu
+9. Click Checkout Button
+10. Enter First Name, Last Name, ZIP
+11. Click Continue Button
+12. Verify product names, total amount
+13. Click Finish Button
+14. Verify the successful order message
+15. Click Reset App State
+16. Logout</t>
   </si>
 </sst>
 </file>
@@ -268,10 +254,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,112 +540,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.453125" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="5" max="5" width="30.7265625" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" customWidth="1"/>
-    <col min="7" max="7" width="21.26953125" customWidth="1"/>
+    <col min="5" max="5" width="33.453125" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" customWidth="1"/>
+    <col min="7" max="7" width="23.1796875" customWidth="1"/>
     <col min="8" max="8" width="24.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>23</v>
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:12" s="3" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
+    <row r="14" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:12" s="3" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Manual-Testing/Q3_TestCases.xlsx
+++ b/Manual-Testing/Q3_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright\ecommerce-automation-test\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187F8240-B95B-4046-9991-07FD235A176B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20A9F8F-7B4C-44CD-BE4F-59174587A128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
